--- a/pre-processing/process_data_3.xlsx
+++ b/pre-processing/process_data_3.xlsx
@@ -5347,7 +5347,7 @@
         <v>2</v>
       </c>
       <c r="B11">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -5511,7 +5511,7 @@
         <v>2</v>
       </c>
       <c r="B15">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C15">
         <v>1</v>
@@ -5716,7 +5716,7 @@
         <v>2</v>
       </c>
       <c r="B20">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -6003,7 +6003,7 @@
         <v>8</v>
       </c>
       <c r="B27">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C27">
         <v>1</v>
@@ -6082,10 +6082,10 @@
     </row>
     <row r="29" spans="1:13">
       <c r="A29">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="B29">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C29">
         <v>1</v>
@@ -6167,7 +6167,7 @@
         <v>8</v>
       </c>
       <c r="B31">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -6782,7 +6782,7 @@
         <v>2</v>
       </c>
       <c r="B46">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C46">
         <v>1</v>
@@ -6823,7 +6823,7 @@
         <v>2</v>
       </c>
       <c r="B47">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C47">
         <v>1</v>
@@ -6905,7 +6905,7 @@
         <v>2</v>
       </c>
       <c r="B49">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C49">
         <v>1</v>
@@ -6946,7 +6946,7 @@
         <v>2</v>
       </c>
       <c r="B50">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C50">
         <v>1</v>
@@ -7028,7 +7028,7 @@
         <v>2</v>
       </c>
       <c r="B52">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C52">
         <v>1</v>
@@ -7274,7 +7274,7 @@
         <v>2</v>
       </c>
       <c r="B58">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C58">
         <v>1</v>
@@ -7725,7 +7725,7 @@
         <v>2</v>
       </c>
       <c r="B69">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C69">
         <v>1</v>
@@ -7766,7 +7766,7 @@
         <v>2</v>
       </c>
       <c r="B70">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C70">
         <v>1</v>
@@ -7930,7 +7930,7 @@
         <v>8</v>
       </c>
       <c r="B74">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C74">
         <v>1</v>
@@ -8258,7 +8258,7 @@
         <v>2</v>
       </c>
       <c r="B82">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C82">
         <v>1</v>
@@ -8296,10 +8296,10 @@
     </row>
     <row r="83" spans="1:13">
       <c r="A83">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="B83">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C83">
         <v>1</v>
@@ -8381,7 +8381,7 @@
         <v>2</v>
       </c>
       <c r="B85">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C85">
         <v>1</v>
@@ -8832,7 +8832,7 @@
         <v>2</v>
       </c>
       <c r="B96">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C96">
         <v>1</v>
@@ -9037,7 +9037,7 @@
         <v>2</v>
       </c>
       <c r="B101">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C101">
         <v>1</v>
@@ -9160,7 +9160,7 @@
         <v>13</v>
       </c>
       <c r="B104">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C104">
         <v>1</v>
@@ -9242,7 +9242,7 @@
         <v>14</v>
       </c>
       <c r="B106">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C106">
         <v>1</v>
@@ -9324,7 +9324,7 @@
         <v>15</v>
       </c>
       <c r="B108">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C108">
         <v>1</v>
@@ -9362,10 +9362,10 @@
     </row>
     <row r="109" spans="1:13">
       <c r="A109">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B109">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C109">
         <v>1</v>
@@ -9406,7 +9406,7 @@
         <v>15</v>
       </c>
       <c r="B110">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C110">
         <v>1</v>
@@ -9526,10 +9526,10 @@
     </row>
     <row r="113" spans="1:13">
       <c r="A113">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="B113">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C113">
         <v>1</v>
@@ -9611,7 +9611,7 @@
         <v>13</v>
       </c>
       <c r="B115">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C115">
         <v>1</v>
@@ -9649,7 +9649,7 @@
     </row>
     <row r="116" spans="1:13">
       <c r="A116">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B116">
         <v>2</v>
@@ -9690,10 +9690,10 @@
     </row>
     <row r="117" spans="1:13">
       <c r="A117">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B117">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C117">
         <v>1</v>
@@ -10018,7 +10018,7 @@
     </row>
     <row r="125" spans="1:13">
       <c r="A125">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B125">
         <v>2</v>
@@ -10059,7 +10059,7 @@
     </row>
     <row r="126" spans="1:13">
       <c r="A126">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B126">
         <v>2</v>
@@ -10428,7 +10428,7 @@
     </row>
     <row r="135" spans="1:13">
       <c r="A135">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B135">
         <v>2</v>
@@ -10469,7 +10469,7 @@
     </row>
     <row r="136" spans="1:13">
       <c r="A136">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B136">
         <v>2</v>
@@ -10920,10 +10920,10 @@
     </row>
     <row r="147" spans="1:13">
       <c r="A147">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B147">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C147">
         <v>1</v>
@@ -11002,10 +11002,10 @@
     </row>
     <row r="149" spans="1:13">
       <c r="A149">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="B149">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="C149">
         <v>1</v>
@@ -11046,7 +11046,7 @@
         <v>14</v>
       </c>
       <c r="B150">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C150">
         <v>1</v>
@@ -11166,7 +11166,7 @@
     </row>
     <row r="153" spans="1:13">
       <c r="A153">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B153">
         <v>2</v>
@@ -11251,7 +11251,7 @@
         <v>14</v>
       </c>
       <c r="B155">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C155">
         <v>1</v>
@@ -11289,7 +11289,7 @@
     </row>
     <row r="156" spans="1:13">
       <c r="A156">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B156">
         <v>2</v>
@@ -11333,7 +11333,7 @@
         <v>14</v>
       </c>
       <c r="B157">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C157">
         <v>1</v>
@@ -11453,7 +11453,7 @@
     </row>
     <row r="160" spans="1:13">
       <c r="A160">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B160">
         <v>2</v>
@@ -11535,7 +11535,7 @@
     </row>
     <row r="162" spans="1:13">
       <c r="A162">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B162">
         <v>2</v>
@@ -11576,10 +11576,10 @@
     </row>
     <row r="163" spans="1:13">
       <c r="A163">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B163">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C163">
         <v>1</v>
@@ -11907,7 +11907,7 @@
         <v>13</v>
       </c>
       <c r="B171">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C171">
         <v>1</v>
@@ -12355,7 +12355,7 @@
     </row>
     <row r="182" spans="1:13">
       <c r="A182">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B182">
         <v>2</v>
@@ -12604,7 +12604,7 @@
         <v>13</v>
       </c>
       <c r="B188">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C188">
         <v>1</v>
@@ -12642,10 +12642,10 @@
     </row>
     <row r="189" spans="1:13">
       <c r="A189">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="B189">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C189">
         <v>1</v>
@@ -12727,7 +12727,7 @@
         <v>13</v>
       </c>
       <c r="B191">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C191">
         <v>1</v>
@@ -12806,7 +12806,7 @@
     </row>
     <row r="193" spans="1:13">
       <c r="A193">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B193">
         <v>2</v>
@@ -12850,7 +12850,7 @@
         <v>14</v>
       </c>
       <c r="B194">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C194">
         <v>1</v>
@@ -12891,7 +12891,7 @@
         <v>14</v>
       </c>
       <c r="B195">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C195">
         <v>1</v>
@@ -12970,7 +12970,7 @@
     </row>
     <row r="197" spans="1:13">
       <c r="A197">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B197">
         <v>2</v>
@@ -13052,10 +13052,10 @@
     </row>
     <row r="199" spans="1:13">
       <c r="A199">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="B199">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C199">
         <v>1</v>
@@ -13585,10 +13585,10 @@
     </row>
     <row r="212" spans="1:13">
       <c r="A212">
-        <v>-1</v>
+        <v>23</v>
       </c>
       <c r="B212">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="C212">
         <v>1</v>
@@ -13667,10 +13667,10 @@
     </row>
     <row r="214" spans="1:13">
       <c r="A214">
-        <v>-1</v>
+        <v>25</v>
       </c>
       <c r="B214">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="C214">
         <v>1</v>
@@ -13831,7 +13831,7 @@
     </row>
     <row r="218" spans="1:13">
       <c r="A218">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B218">
         <v>3</v>
@@ -13913,7 +13913,7 @@
     </row>
     <row r="220" spans="1:13">
       <c r="A220">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B220">
         <v>4</v>
@@ -13954,7 +13954,7 @@
     </row>
     <row r="221" spans="1:13">
       <c r="A221">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B221">
         <v>4</v>
@@ -14036,7 +14036,7 @@
     </row>
     <row r="223" spans="1:13">
       <c r="A223">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B223">
         <v>3</v>
@@ -14118,7 +14118,7 @@
     </row>
     <row r="225" spans="1:13">
       <c r="A225">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B225">
         <v>4</v>
@@ -14159,7 +14159,7 @@
     </row>
     <row r="226" spans="1:13">
       <c r="A226">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B226">
         <v>3</v>
@@ -14200,10 +14200,10 @@
     </row>
     <row r="227" spans="1:13">
       <c r="A227">
-        <v>-1</v>
+        <v>29</v>
       </c>
       <c r="B227">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="C227">
         <v>1</v>
@@ -14282,7 +14282,7 @@
     </row>
     <row r="229" spans="1:13">
       <c r="A229">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B229">
         <v>2</v>
@@ -14323,7 +14323,7 @@
     </row>
     <row r="230" spans="1:13">
       <c r="A230">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B230">
         <v>3</v>
@@ -14528,10 +14528,10 @@
     </row>
     <row r="235" spans="1:13">
       <c r="A235">
-        <v>-1</v>
+        <v>23</v>
       </c>
       <c r="B235">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="C235">
         <v>1</v>
@@ -14610,7 +14610,7 @@
     </row>
     <row r="237" spans="1:13">
       <c r="A237">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B237">
         <v>2</v>
@@ -15020,7 +15020,7 @@
     </row>
     <row r="247" spans="1:13">
       <c r="A247">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B247">
         <v>2</v>
@@ -15225,10 +15225,10 @@
     </row>
     <row r="252" spans="1:13">
       <c r="A252">
-        <v>-1</v>
+        <v>29</v>
       </c>
       <c r="B252">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="C252">
         <v>1</v>
@@ -15348,7 +15348,7 @@
     </row>
     <row r="255" spans="1:13">
       <c r="A255">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B255">
         <v>4</v>
@@ -15594,7 +15594,7 @@
     </row>
     <row r="261" spans="1:13">
       <c r="A261">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B261">
         <v>2</v>
@@ -15717,7 +15717,7 @@
     </row>
     <row r="264" spans="1:13">
       <c r="A264">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B264">
         <v>3</v>
@@ -15758,7 +15758,7 @@
     </row>
     <row r="265" spans="1:13">
       <c r="A265">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B265">
         <v>3</v>
@@ -16168,7 +16168,7 @@
     </row>
     <row r="275" spans="1:13">
       <c r="A275">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B275">
         <v>2</v>
@@ -16250,7 +16250,7 @@
     </row>
     <row r="277" spans="1:13">
       <c r="A277">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B277">
         <v>2</v>
@@ -16824,7 +16824,7 @@
     </row>
     <row r="291" spans="1:13">
       <c r="A291">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B291">
         <v>2</v>
@@ -17152,10 +17152,10 @@
     </row>
     <row r="299" spans="1:13">
       <c r="A299">
-        <v>-1</v>
+        <v>25</v>
       </c>
       <c r="B299">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="C299">
         <v>1</v>
@@ -17234,7 +17234,7 @@
     </row>
     <row r="301" spans="1:13">
       <c r="A301">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B301">
         <v>2</v>
@@ -17685,10 +17685,10 @@
     </row>
     <row r="312" spans="1:13">
       <c r="A312">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B312">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C312">
         <v>1</v>
@@ -18628,7 +18628,7 @@
     </row>
     <row r="335" spans="1:13">
       <c r="A335">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B335">
         <v>2</v>
@@ -18669,7 +18669,7 @@
     </row>
     <row r="336" spans="1:13">
       <c r="A336">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B336">
         <v>2</v>
@@ -19284,10 +19284,10 @@
     </row>
     <row r="351" spans="1:13">
       <c r="A351">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B351">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C351">
         <v>1</v>
@@ -19653,10 +19653,10 @@
     </row>
     <row r="360" spans="1:13">
       <c r="A360">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B360">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C360">
         <v>1</v>
@@ -19694,10 +19694,10 @@
     </row>
     <row r="361" spans="1:13">
       <c r="A361">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B361">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C361">
         <v>1</v>
@@ -20227,7 +20227,7 @@
     </row>
     <row r="374" spans="1:13">
       <c r="A374">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B374">
         <v>2</v>
@@ -20432,7 +20432,7 @@
     </row>
     <row r="379" spans="1:13">
       <c r="A379">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B379">
         <v>2</v>
@@ -21211,10 +21211,10 @@
     </row>
     <row r="398" spans="1:13">
       <c r="A398">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B398">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C398">
         <v>1</v>
@@ -21293,10 +21293,10 @@
     </row>
     <row r="400" spans="1:13">
       <c r="A400">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B400">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C400">
         <v>1</v>
@@ -21457,7 +21457,7 @@
     </row>
     <row r="404" spans="1:13">
       <c r="A404">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B404">
         <v>2</v>
@@ -21498,7 +21498,7 @@
     </row>
     <row r="405" spans="1:13">
       <c r="A405">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B405">
         <v>2</v>
@@ -21621,7 +21621,7 @@
     </row>
     <row r="408" spans="1:13">
       <c r="A408">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B408">
         <v>2</v>
@@ -21662,7 +21662,7 @@
     </row>
     <row r="409" spans="1:13">
       <c r="A409">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B409">
         <v>2</v>
@@ -21744,7 +21744,7 @@
     </row>
     <row r="411" spans="1:13">
       <c r="A411">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B411">
         <v>2</v>
@@ -21785,7 +21785,7 @@
     </row>
     <row r="412" spans="1:13">
       <c r="A412">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B412">
         <v>2</v>
@@ -21826,7 +21826,7 @@
     </row>
     <row r="413" spans="1:13">
       <c r="A413">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B413">
         <v>2</v>
@@ -21867,7 +21867,7 @@
     </row>
     <row r="414" spans="1:13">
       <c r="A414">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B414">
         <v>2</v>
@@ -21908,7 +21908,7 @@
     </row>
     <row r="415" spans="1:13">
       <c r="A415">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B415">
         <v>2</v>
@@ -21949,7 +21949,7 @@
     </row>
     <row r="416" spans="1:13">
       <c r="A416">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B416">
         <v>2</v>
@@ -21990,7 +21990,7 @@
     </row>
     <row r="417" spans="1:13">
       <c r="A417">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B417">
         <v>2</v>
@@ -22031,7 +22031,7 @@
     </row>
     <row r="418" spans="1:13">
       <c r="A418">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B418">
         <v>2</v>
@@ -22072,10 +22072,10 @@
     </row>
     <row r="419" spans="1:13">
       <c r="A419">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B419">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C419">
         <v>1</v>
@@ -22154,7 +22154,7 @@
     </row>
     <row r="421" spans="1:13">
       <c r="A421">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B421">
         <v>2</v>
@@ -22236,10 +22236,10 @@
     </row>
     <row r="423" spans="1:13">
       <c r="A423">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B423">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C423">
         <v>1</v>
@@ -22359,7 +22359,7 @@
     </row>
     <row r="426" spans="1:13">
       <c r="A426">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B426">
         <v>2</v>
@@ -22441,10 +22441,10 @@
     </row>
     <row r="428" spans="1:13">
       <c r="A428">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B428">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C428">
         <v>1</v>
@@ -22523,7 +22523,7 @@
     </row>
     <row r="430" spans="1:13">
       <c r="A430">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B430">
         <v>2</v>
@@ -22564,10 +22564,10 @@
     </row>
     <row r="431" spans="1:13">
       <c r="A431">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B431">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C431">
         <v>1</v>
@@ -22605,7 +22605,7 @@
     </row>
     <row r="432" spans="1:13">
       <c r="A432">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B432">
         <v>2</v>
@@ -22646,10 +22646,10 @@
     </row>
     <row r="433" spans="1:13">
       <c r="A433">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B433">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C433">
         <v>1</v>
@@ -23097,10 +23097,10 @@
     </row>
     <row r="444" spans="1:13">
       <c r="A444">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B444">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C444">
         <v>1</v>
@@ -23261,10 +23261,10 @@
     </row>
     <row r="448" spans="1:13">
       <c r="A448">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B448">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C448">
         <v>1</v>
@@ -23302,7 +23302,7 @@
     </row>
     <row r="449" spans="1:13">
       <c r="A449">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B449">
         <v>3</v>
@@ -23466,7 +23466,7 @@
     </row>
     <row r="453" spans="1:13">
       <c r="A453">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B453">
         <v>3</v>
@@ -23507,7 +23507,7 @@
     </row>
     <row r="454" spans="1:13">
       <c r="A454">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B454">
         <v>2</v>
@@ -23589,7 +23589,7 @@
     </row>
     <row r="456" spans="1:13">
       <c r="A456">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B456">
         <v>2</v>
@@ -23630,7 +23630,7 @@
     </row>
     <row r="457" spans="1:13">
       <c r="A457">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B457">
         <v>3</v>
@@ -23671,10 +23671,10 @@
     </row>
     <row r="458" spans="1:13">
       <c r="A458">
-        <v>-1</v>
+        <v>54</v>
       </c>
       <c r="B458">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="C458">
         <v>1</v>
@@ -23753,7 +23753,7 @@
     </row>
     <row r="460" spans="1:13">
       <c r="A460">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B460">
         <v>2</v>
@@ -23835,10 +23835,10 @@
     </row>
     <row r="462" spans="1:13">
       <c r="A462">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B462">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C462">
         <v>1</v>
@@ -23876,10 +23876,10 @@
     </row>
     <row r="463" spans="1:13">
       <c r="A463">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B463">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C463">
         <v>1</v>
@@ -24778,10 +24778,10 @@
     </row>
     <row r="485" spans="1:13">
       <c r="A485">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B485">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C485">
         <v>1</v>
@@ -24819,10 +24819,10 @@
     </row>
     <row r="486" spans="1:13">
       <c r="A486">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B486">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C486">
         <v>1</v>
@@ -24901,7 +24901,7 @@
     </row>
     <row r="488" spans="1:13">
       <c r="A488">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B488">
         <v>3</v>
@@ -24942,7 +24942,7 @@
     </row>
     <row r="489" spans="1:13">
       <c r="A489">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B489">
         <v>3</v>
@@ -25147,7 +25147,7 @@
     </row>
     <row r="494" spans="1:13">
       <c r="A494">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B494">
         <v>2</v>
@@ -25188,7 +25188,7 @@
     </row>
     <row r="495" spans="1:13">
       <c r="A495">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B495">
         <v>3</v>
@@ -25229,10 +25229,10 @@
     </row>
     <row r="496" spans="1:13">
       <c r="A496">
-        <v>-1</v>
+        <v>54</v>
       </c>
       <c r="B496">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="C496">
         <v>1</v>
@@ -25270,10 +25270,10 @@
     </row>
     <row r="497" spans="1:13">
       <c r="A497">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B497">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C497">
         <v>1</v>
@@ -25311,10 +25311,10 @@
     </row>
     <row r="498" spans="1:13">
       <c r="A498">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B498">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C498">
         <v>1</v>
